--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_xgb_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_xgb_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>0.6701720817343015</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>0.3840428795918789</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,11 +987,11 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -998,15 +999,15 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,27 +1096,27 @@
         <v>0.5636957583315323</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,27 +1124,27 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>0.6062674327381511</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,19 +1267,19 @@
         <v>0.3780552339532941</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1286,31 +1287,31 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -1393,27 +1394,27 @@
         <v>0.7799234338213668</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>0.7073524601517669</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1564,19 +1565,19 @@
         <v>0.2931325055089278</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1584,31 +1585,31 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -1691,19 +1692,19 @@
         <v>0.741043874298282</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,27 +1720,27 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,19 +1833,19 @@
         <v>0.6724025795063587</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
@@ -1852,7 +1853,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,19 +1863,19 @@
         <v>0.05985288865881788</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,31 +1883,31 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766684</v>
+        <v>0.05644008609220896</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208207</v>
+        <v>0.08831268540851259</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571159</v>
+        <v>0.2970580221997939</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798217</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278889</v>
+        <v>0.2724034021441999</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668931</v>
+        <v>-0.08310591627223018</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.0885112574001572</v>
+        <v>0.07356843507801791</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.005427261428731622</v>
+        <v>0.01621327059745248</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2850465641718551</v>
+        <v>0.09749194666774841</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1968916734512504</v>
+        <v>0.3220812091790823</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5046718081597295</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.06460870262993701</v>
+        <v>-0.01250556989261897</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.072722551490211</v>
+        <v>1.061174210396038</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.8401713401642454</v>
+        <v>0.3094081175441943</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.07487343987011807</v>
+        <v>0.02908253415358342</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.180034412920183</v>
+        <v>1.135845276192276</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1423032147182204</v>
+        <v>-0.1018465904642569</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.4019713384400463</v>
+        <v>-0.01468781445418832</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.5105668491253068</v>
+        <v>0.0209157393028323</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.07189056925758908</v>
+        <v>-0.03487413543191487</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.05363172212770406</v>
+        <v>0.07356843507801791</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.1622195726868854</v>
+        <v>0.01621327059745248</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2148226548093675</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1581365123087654</v>
+        <v>0.09749194666774841</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1078562844095457</v>
+        <v>0.3220812091790823</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9922437673130194</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1706701819990795</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.5661290982155851</v>
+        <v>-0.01250556989261897</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.3627738861914108</v>
+        <v>1.061174210396038</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2148226548093675</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2704616417476196</v>
+        <v>0.3094081175441943</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2579030847386118</v>
+        <v>0.02908253415358342</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3798678071721532</v>
+        <v>1.135845276192276</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07955526879738462</v>
+        <v>-0.1018465904642569</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.1559459518089343</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.6743036872578336</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3095960066228268</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0120677062654222</v>
+        <v>0.07356843507801791</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1163719470506128</v>
+        <v>0.01621327059745248</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4523724087433373</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2356087063787287</v>
+        <v>0.09749194666774841</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.170120292236529</v>
+        <v>0.3220812091790823</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9977839335180055</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4126450791225487</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1091770880536074</v>
+        <v>-0.01250556989261897</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8771119665874416</v>
+        <v>1.061174210396038</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4523724087433373</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.723093942506672</v>
+        <v>0.3094081175441943</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.006486663919132107</v>
+        <v>0.02908253415358342</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.015597289673311</v>
+        <v>1.135845276192276</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.1018465904642569</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1103458100631036</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1857894029719529</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.06362309590536475</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.208011048714755</v>
+        <v>0.01490676221166587</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.2150036897350264</v>
+        <v>-0.02048723366447003</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.008907864825391298</v>
+        <v>0.03613428746676672</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,49 +2650,49 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.0885112574001572</v>
+        <v>0.07356843507801791</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.005427261428731622</v>
+        <v>0.01621327059745248</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2850465641718551</v>
+        <v>0.09749194666774841</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1968916734512504</v>
+        <v>0.3220812091790823</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.5046718081597295</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.06460870262993701</v>
+        <v>-0.01250556989261897</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.072722551490211</v>
+        <v>1.061174210396038</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.8401713401642454</v>
+        <v>0.3094081175441943</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.07487343987011807</v>
+        <v>0.02908253415358342</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.180034412920183</v>
+        <v>1.135845276192276</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1423032147182204</v>
+        <v>-0.1018465904642569</v>
       </c>
       <c r="Y7" s="2" t="n">
         <v>0</v>
@@ -2755,49 +2756,49 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.0885112574001572</v>
+        <v>0.07356843507801791</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.005427261428731622</v>
+        <v>0.01621327059745248</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2850465641718551</v>
+        <v>0.09749194666774841</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1968916734512504</v>
+        <v>0.3220812091790823</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.5046718081597295</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.06460870262993701</v>
+        <v>-0.01250556989261897</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.072722551490211</v>
+        <v>1.061174210396038</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.8401713401642454</v>
+        <v>0.3094081175441943</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.07487343987011807</v>
+        <v>0.02908253415358342</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.180034412920183</v>
+        <v>1.135845276192276</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1423032147182204</v>
+        <v>-0.1018465904642569</v>
       </c>
       <c r="Y8" s="2" t="n">
         <v>0</v>
@@ -2809,13 +2810,13 @@
         <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.2867186563794621</v>
+        <v>0.01490676221166587</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.3379968582131604</v>
+        <v>-0.02048723366447003</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.07745915177274143</v>
+        <v>0.03613428746676672</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,64 +2864,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.2109675743625575</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1296494692580091</v>
+        <v>-0.03796582501302292</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4686364820397299</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.3162415185039309</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1594393241536228</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4643360036641077</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.01156253316718003</v>
+        <v>0.2117597153840098</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.9869853923793556</v>
+        <v>-0.03587709265072057</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4686364820397299</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4729988034190624</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1395978971097885</v>
+        <v>-0.2060850325577082</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6643345691790064</v>
+        <v>0.03737143334716829</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1115198401367691</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1343475911870482</v>
+        <v>-0.05331469011285639</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.0814324828670947</v>
+        <v>0.227105367320646</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1995317113853163</v>
+        <v>-0.2285215800545249</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.2791458357934953</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.1971069850667453</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2969,70 +2974,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.1454729763806552</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.05740496287003616</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4989302081758815</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.3036688481624587</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1818261007142053</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4948749056728245</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.04610796417330365</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.051898407833811</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4989302081758815</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.6917136630433527</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.01184305799024898</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9715231730216646</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1364098565690741</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.06249305813478923</v>
+        <v>-0.01468781445418832</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.01977860870488102</v>
+        <v>0.0209157393028323</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.08067600765244076</v>
+        <v>-0.03487413543191487</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.331293788852801</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.3249033571103567</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.009465951000868555</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.2791458357934953</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.01828253075611685</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3275,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.0534149946425504</v>
+        <v>-0.09123360655355228</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360385</v>
+        <v>0.2716992530341478</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019929</v>
+        <v>0.1810585772249195</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573141</v>
+        <v>-0.4707583434268607</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3305,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.121721302370637</v>
+        <v>0.717110477150922</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3317,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756414</v>
+        <v>-0.1395291740668931</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3363,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1019213862233868</v>
+        <v>-0.08568579969177081</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.04604680190383625</v>
+        <v>0.006104766749507107</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2007330591320373</v>
+        <v>0.2851956016709155</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2406643520933329</v>
+        <v>0.1969993142200973</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9738372093023255</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5031043706109168</v>
+        <v>-0.5038864433233314</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.0008154879999826559</v>
+        <v>-0.06259541267211743</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9991958792334011</v>
+        <v>1.070371774306359</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.217611347433591</v>
+        <v>0.8429534690262739</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.04519445836539138</v>
+        <v>0.07328765012496707</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.085484732134711</v>
+        <v>1.175486198968011</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1903416370175206</v>
+        <v>-0.1423032147182204</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3457,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.1975871140978549</v>
+        <v>0.2834444878548723</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.1368616548924535</v>
+        <v>0.412293078958915</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1847647558521955</v>
+        <v>0.1114874581688012</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118271660599822</v>
+        <v>0.1527921426208967</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9614825581395349</v>
+        <v>0.9584026622296173</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2500855498878848</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07708757922255405</v>
+        <v>0.4169603635659389</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9239869583598836</v>
+        <v>0.5312397610786888</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.239468393809461</v>
+        <v>0.711454536798154</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.05549602170052359</v>
+        <v>-0.003293870969882207</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.104970005642202</v>
+        <v>0.9921128744691625</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.08681719864095117</v>
+        <v>0.4037236733523375</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.07620994292863381</v>
+        <v>0.5115782264358801</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.009856121272632024</v>
+        <v>-0.07135228015148831</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3559,58 +3568,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.01815629109767514</v>
+        <v>0.05689779852772059</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.03347085785202764</v>
+        <v>0.1630027322197649</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.08642977100026483</v>
+        <v>-0.2148226548093674</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0405466782340818</v>
+        <v>0.1582241384653827</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.04644970282817998</v>
+        <v>0.1079128955777404</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9934593023255814</v>
+        <v>0.9922351636161952</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.03144220484002103</v>
+        <v>-0.1693552427576553</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.9508073428035633</v>
+        <v>0.5694999570154822</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.06244613115169745</v>
+        <v>0.359749848563156</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.08642977100026483</v>
+        <v>-0.2148226548093674</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.05120860746312395</v>
+        <v>0.2723824346240535</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.5045491571920451</v>
+        <v>-0.2589979203113207</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.04565180972751438</v>
+        <v>0.3798332938966785</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02183160636802017</v>
+        <v>-0.07955526879738462</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.07601730592851053</v>
+        <v>0.1559459518089343</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.9492177790953584</v>
+        <v>0.6743036872578341</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5259725701351265</v>
+        <v>-0.309596006622827</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3665,67 +3674,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.163012261054118</v>
+        <v>0.01520494139343964</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1040399718714433</v>
+        <v>0.1171242122448317</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4691960268712783</v>
+        <v>-0.4523724087433373</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1891162085682249</v>
+        <v>0.2357392680705751</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.212988509005488</v>
+        <v>0.1702126846542851</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9680232558139535</v>
+        <v>0.9977814753189129</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4635884392739443</v>
+        <v>-0.4117138018220807</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.08040595683427099</v>
+        <v>0.1115644259507005</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.920714836208417</v>
+        <v>0.874575687443013</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4691960268712783</v>
+        <v>-0.4523724087433373</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.168134220448067</v>
+        <v>0.7256990637172904</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.02187512470444264</v>
+        <v>0.005001767027022597</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.041376514807503</v>
+        <v>1.011976657488663</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.05544032051152747</v>
+        <v>0.1103458100631038</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.07952561664822055</v>
+        <v>0.1857894029719536</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.02231100009601894</v>
+        <v>-0.06362309590536486</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.02887042841119924</v>
+        <v>-0.2089997261274337</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0.003080880028448529</v>
+        <v>-0.2155289205455794</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.03185317263623022</v>
+        <v>0.008323053059759111</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -3773,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3707258300542482</v>
+        <v>-0.08568579969177081</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3012211113620697</v>
+        <v>0.006104766749507107</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2760089111735863</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.07329327005720059</v>
+        <v>0.2851956016709155</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1658799359567353</v>
+        <v>0.1969993142200973</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9425872093023255</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2683604314036379</v>
+        <v>-0.5038864433233314</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4736217599360357</v>
+        <v>-0.06259541267211743</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5329801386583189</v>
+        <v>1.070371774306359</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2760089111735863</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.8734987675474708</v>
+        <v>0.8429534690262739</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1169911121436273</v>
+        <v>0.07328765012496707</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7787128279559508</v>
+        <v>1.175486198968011</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1903416370175206</v>
+        <v>-0.1423032147182204</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.2439415798545614</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.4724210182647188</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1551726276492751</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3879,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1231350435471563</v>
+        <v>-0.08568579969177081</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.06618478876718825</v>
+        <v>0.006104766749507107</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4773061338280115</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.169389886206707</v>
+        <v>0.2851956016709155</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2315136794492334</v>
+        <v>0.1969993142200973</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9731104651162791</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4717842240655957</v>
+        <v>-0.5038864433233314</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06389852977985289</v>
+        <v>-0.06259541267211743</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9369921632786584</v>
+        <v>1.070371774306359</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4773061338280115</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.126280763879781</v>
+        <v>0.8429534690262739</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.002148944587608836</v>
+        <v>0.07328765012496707</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.004064700830329</v>
+        <v>1.175486198968011</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1903416370175206</v>
+        <v>-0.1423032147182204</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.01925151611447995</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.06303164023364061</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.04118421546656736</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.06216839649847394</v>
+        <v>-0.2876090793483412</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.01224510401672363</v>
+        <v>-0.3384397958960551</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.05054218681655154</v>
+        <v>0.07683460436765821</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -3987,58 +3996,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.286094244985885</v>
+        <v>-0.2085217100912933</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2208808983417674</v>
+        <v>-0.1290629851450956</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1903416370175204</v>
+        <v>-0.4686364820397297</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.05868506810158925</v>
+        <v>0.3163754031655423</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1440488598178875</v>
+        <v>0.1595260172952468</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03144220484002103</v>
+        <v>-0.4634866846191248</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.9508073428035633</v>
+        <v>0.01373977032499707</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.06244613115169745</v>
+        <v>0.984553308700166</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.08642977100026483</v>
+        <v>-0.4686364820397297</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3278446071186261</v>
+        <v>0.4752258093479558</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3741663404920327</v>
+        <v>-0.1408672715131923</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2922692173410292</v>
+        <v>0.662695392815939</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1903416370175206</v>
+        <v>-0.1115198401367691</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1671379293160953</v>
+        <v>-0.1343475911870478</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.9492177790953584</v>
+        <v>0.08143248286709559</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.4012275376136935</v>
+        <v>-0.1995317113853163</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4093,67 +4102,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.08326425458987696</v>
+        <v>-0.1428240901650962</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02833570824331688</v>
+        <v>-0.05676979692865824</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4691960268712783</v>
+        <v>-0.4989302081758814</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1956675178865194</v>
+        <v>0.3038159612110616</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2279931225042153</v>
+        <v>0.1819253327785926</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9803779069767442</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4635884392739443</v>
+        <v>-0.4940740074126367</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.08040595683427099</v>
+        <v>-0.0440548541411987</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.920714836208417</v>
+        <v>1.04952788264155</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4691960268712783</v>
+        <v>-0.4989302081758814</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>1.019464780221427</v>
+        <v>0.6942713408560182</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04819507728699179</v>
+        <v>-0.01330091254978494</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.908839636072613</v>
+        <v>0.968151160772823</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1903416370175204</v>
+        <v>-0.1364098565690741</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.01693145433673204</v>
+        <v>-0.06249305813478911</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.07952561664822055</v>
+        <v>0.01977860870488124</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.08935134979421688</v>
+        <v>-0.08067600765244065</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.09546099666753483</v>
+        <v>-0.3321285665673213</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0.003080880028448529</v>
+        <v>-0.3253550554843618</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.09823921346520792</v>
+        <v>-0.01004011241471992</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -4399,28 +4408,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.0534149946425504</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702552</v>
+        <v>0.2216991067360385</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962864</v>
+        <v>0.2389480542019929</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573141</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4429,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.121721302370637</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4441,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756414</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4487,49 +4496,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.05429070103913802</v>
+        <v>0.1019213862233868</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.03017445041727607</v>
+        <v>0.04604680190383625</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.05847802996069337</v>
+        <v>0.2007330591320373</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1943365262252255</v>
+        <v>0.2406643520933329</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.9738372093023255</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.5031043706109168</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.0327416689383877</v>
+        <v>0.0008154879999826559</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8652110026700077</v>
+        <v>0.9991958792334011</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2688449302478968</v>
+        <v>1.217611347433591</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.002485828352167374</v>
+        <v>0.04519445836539138</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9883753293641022</v>
+        <v>1.085484732134711</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02892173456683256</v>
+        <v>-0.1903416370175206</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4581,58 +4590,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>0.1975871140978549</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>0.1368616548924535</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.1847647558521955</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.2118271660599822</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9614825581395349</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.07708757922255405</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.9239869583598836</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>1.239468393809461</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>0.05549602170052359</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>1.104970005642202</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03557401440791119</v>
+        <v>0.08681719864095117</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02726155965049526</v>
+        <v>0.07620994292863381</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.06116803794331138</v>
+        <v>0.009856121272632024</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4683,58 +4692,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.05429070103913758</v>
+        <v>0.01815629109767514</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03017445041727562</v>
+        <v>-0.03347085785202764</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1775169494986037</v>
+        <v>-0.08642977100026483</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.05847802996069347</v>
+        <v>0.0405466782340818</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1943365262252257</v>
+        <v>0.04644970282817998</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.9934593023255814</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1690941297033368</v>
+        <v>-0.03144220484002103</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.03274166893838726</v>
+        <v>0.9508073428035633</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8652110026700094</v>
+        <v>0.06244613115169745</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1775169494986037</v>
+        <v>-0.08642977100026483</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.268844930247897</v>
+        <v>0.05120860746312395</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.002485828352167152</v>
+        <v>-0.5045491571920451</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9883753293641031</v>
+        <v>0.04565180972751438</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02892173456683256</v>
+        <v>-0.02183160636802017</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>-0.07601730592851053</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0.9492177790953584</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.5259725701351265</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -4789,67 +4798,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.05429070103913802</v>
+        <v>0.163012261054118</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.03017445041727607</v>
+        <v>0.1040399718714433</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4691960268712783</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.05847802996069337</v>
+        <v>0.1891162085682249</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1943365262252255</v>
+        <v>0.212988509005488</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.9680232558139535</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4635884392739443</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.0327416689383877</v>
+        <v>0.08040595683427099</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8652110026700077</v>
+        <v>0.920714836208417</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4691960268712783</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2688449302478968</v>
+        <v>1.168134220448067</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.002485828352167374</v>
+        <v>0.02187512470444264</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9883753293641022</v>
+        <v>1.041376514807503</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02892173456683256</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>0.05544032051152747</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.07952561664822055</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>-0.02231100009601894</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.03688620478851079</v>
+        <v>-0.02887042841119924</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.02653808992888873</v>
+        <v>0.003080880028448529</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.06515333991112882</v>
+        <v>-0.03185317263623022</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -4897,58 +4906,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.09744015744597778</v>
+        <v>0.3707258300542482</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1180856581060969</v>
+        <v>0.3012211113620697</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.2760089111735863</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.0920834020571073</v>
+        <v>0.07329327005720059</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1659425623603643</v>
+        <v>0.1658799359567353</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9425872093023255</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.2683604314036379</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.0327416689383877</v>
+        <v>0.4736217599360357</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.8652110026700077</v>
+        <v>0.5329801386583189</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.2760089111735863</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08623596825928748</v>
+        <v>0.8734987675474708</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1460455519331649</v>
+        <v>-0.1169911121436273</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3170359338846871</v>
+        <v>0.7787128279559508</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1903416370175206</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1439174777275051</v>
+        <v>0.2439415798545614</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.4724210182647188</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.143917477727505</v>
+        <v>-0.1551726276492751</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5003,67 +5012,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.002384270233134589</v>
+        <v>0.1231350435471563</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02520411578394555</v>
+        <v>0.06618478876718825</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4773061338280115</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.06621867918251137</v>
+        <v>0.169389886206707</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1841373437120048</v>
+        <v>0.2315136794492334</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9731104651162791</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4717842240655957</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.0327416689383877</v>
+        <v>0.06389852977985289</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8652110026700077</v>
+        <v>0.9369921632786584</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4773061338280115</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2006362759366236</v>
+        <v>1.126280763879781</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.05610869248831529</v>
+        <v>0.002148944587608836</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7376145986029752</v>
+        <v>1.004064700830329</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0233044746011295</v>
+        <v>-0.1903416370175206</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.05375649355193235</v>
+        <v>0.01925151611447995</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.06303164023364061</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.05375649355193246</v>
+        <v>-0.04118421546656736</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.01885316179329033</v>
+        <v>-0.06216839649847394</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.02653808992888873</v>
+        <v>-0.01224510401672363</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.007894431262376767</v>
+        <v>-0.05054218681655154</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5111,58 +5120,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.09744015744597789</v>
+        <v>0.286094244985885</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1180856581060971</v>
+        <v>0.2208808983417674</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1775169494986037</v>
+        <v>-0.1903416370175204</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.09208340205710734</v>
+        <v>0.05868506810158925</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1659425623603644</v>
+        <v>0.1440488598178875</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1690941297033368</v>
+        <v>-0.03144220484002103</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.03274166893838726</v>
+        <v>0.9508073428035633</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8652110026700094</v>
+        <v>0.06244613115169745</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1775169494986037</v>
+        <v>-0.08642977100026483</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08623596825928792</v>
+        <v>0.3278446071186261</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1460455519331646</v>
+        <v>-0.3741663404920327</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3170359338846888</v>
+        <v>0.2922692173410292</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.1903416370175206</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1439174777275052</v>
+        <v>0.1671379293160953</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0.9492177790953584</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1439174777275046</v>
+        <v>-0.4012275376136935</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5217,67 +5226,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.002384270233134589</v>
+        <v>0.08326425458987696</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.02520411578394555</v>
+        <v>0.02833570824331688</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4691960268712783</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.06621867918251137</v>
+        <v>0.1956675178865194</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1841373437120048</v>
+        <v>0.2279931225042153</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9803779069767442</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.4635884392739443</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.0327416689383877</v>
+        <v>0.08040595683427099</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.8652110026700077</v>
+        <v>0.920714836208417</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.4691960268712783</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.2006362759366236</v>
+        <v>1.019464780221427</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.05610869248831529</v>
+        <v>-0.04819507728699179</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7376145986029752</v>
+        <v>0.908839636072613</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.0233044746011295</v>
+        <v>-0.1903416370175204</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.05375649355193235</v>
+        <v>-0.01693145433673204</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0</v>
+        <v>0.07952561664822055</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.05375649355193246</v>
+        <v>-0.08935134979421688</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.01885316179329033</v>
+        <v>-0.09546099666753483</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.02653808992888873</v>
+        <v>0.003080880028448529</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.007894431262376767</v>
+        <v>-0.09823921346520792</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5523,28 +5532,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.01891210187562642</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570336</v>
+        <v>0.08099293800751969</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886579</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5553,10 +5562,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5565,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886031</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5611,49 +5620,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>0.05158957805580444</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>0.03207094716023584</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.05828083851341805</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.1937034912863763</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02953137989967969</v>
+        <v>0.03464289179502811</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.072223905958428</v>
+        <v>0.8605342385127216</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.2688449302478968</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.002485828352167374</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.9883753293641022</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>-0.02892173456683256</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5705,58 +5714,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.01712918805183983</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.001749821030199383</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.04617799198161064</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.167065999353103</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03008714404519386</v>
+        <v>-0.0327698093658132</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03039102317395725</v>
+        <v>0.03024846801688175</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.05869438481020306</v>
+        <v>-0.06116803794331138</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5807,58 +5816,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>0.051589578055804</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>0.0320709471602354</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3111804093256713</v>
+        <v>-0.1775169494986037</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.05828083851341816</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4729976975805061</v>
+        <v>0.1937034912863764</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3111804093256713</v>
+        <v>-0.1712229343499425</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02953137989967991</v>
+        <v>0.03464289179502766</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.072223905958429</v>
+        <v>0.8605342385127238</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3111804093256713</v>
+        <v>-0.1775169494986037</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.268844930247897</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.002485828352167152</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.9883753293641031</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>-0.02892173456683256</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>-5.551115123125783e-16</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5913,49 +5922,49 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>0.05158957805580444</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>0.03207094716023584</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.05828083851341805</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.1937034912863763</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02953137989967969</v>
+        <v>0.03464289179502811</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.072223905958428</v>
+        <v>0.8605342385127216</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.2688449302478968</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.002485828352167374</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.9883753293641022</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>-0.02892173456683256</v>
       </c>
       <c r="Y6" s="2" t="n">
         <v>0</v>
@@ -5967,13 +5976,13 @@
         <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.03102046112748491</v>
+        <v>0.03388005221831092</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.02949465056512468</v>
+        <v>-0.02936036204461123</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.06235422785443445</v>
+        <v>0.06515333991112882</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -6021,58 +6030,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>-0.09975254162251834</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>-0.1164621003909025</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.09177096240261222</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.1653873768992378</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02953137989967969</v>
+        <v>0.03464289179502811</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.072223905958428</v>
+        <v>0.8605342385127216</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.08623596825928748</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.1460455519331649</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.3170359338846871</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1439174777275052</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0</v>
+        <v>-0.143917477727505</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6127,67 +6136,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>-0.004940190316231829</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>-0.02340956805592032</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.06599487410578811</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.1835318402819057</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02953137989967969</v>
+        <v>0.03464289179502811</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.072223905958428</v>
+        <v>0.8605342385127216</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.2006362759366236</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.05610869248831529</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.7376145986029752</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>-0.0233044746011295</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>-0.05375649355193246</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
+        <v>-0.05375649355193246</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.03102046112748491</v>
+        <v>-0.02169771414223431</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.02949465056512468</v>
+        <v>-0.02936036204461123</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.06235422785443445</v>
+        <v>0.007894431262376767</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -6235,58 +6244,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.03488923518577991</v>
+        <v>-0.09975254162251834</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.05732894814631739</v>
+        <v>-0.1164621003909025</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3111804093256714</v>
+        <v>-0.1775169494986036</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1241006863166953</v>
+        <v>0.09177096240261225</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.1653873768992379</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3111804093256714</v>
+        <v>-0.1712229343499424</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.02953137989968002</v>
+        <v>0.03464289179502789</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.072223905958429</v>
+        <v>0.8605342385127233</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3111804093256714</v>
+        <v>-0.1775169494986036</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5024097008806936</v>
+        <v>0.08623596825928792</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.02864344881523728</v>
+        <v>-0.1460455519331646</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.9189644287180435</v>
+        <v>0.3170359338846888</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.06316869981712392</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>-0.1439174777275052</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-3.33066907387547e-16</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>1.110223024625157e-15</v>
+        <v>-0.1439174777275046</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6341,67 +6350,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>-0.004940190316231829</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>-0.02340956805592032</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.06599487410578811</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.1835318402819057</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.02953137989967969</v>
+        <v>0.03464289179502811</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.072223905958428</v>
+        <v>0.8605342385127216</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.2006362759366236</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.05610869248831529</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.7376145986029752</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>-0.0233044746011295</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
+        <v>-0.05375649355193246</v>
       </c>
       <c r="Z10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0</v>
+        <v>-0.05375649355193246</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.03102046112748491</v>
+        <v>-0.02169771414223431</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.02949465056512468</v>
+        <v>-0.02936036204461123</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.06235422785443445</v>
+        <v>0.007894431262376767</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6647,28 +6656,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363057</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752893</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2405796270435321</v>
+        <v>0.4518304992174231</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450099</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6677,10 +6686,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682997</v>
+        <v>0.5657770181230004</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6689,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174769</v>
+        <v>-0.05185156587886031</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6735,49 +6744,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.3595704026356366</v>
+        <v>0.04240795586410551</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.2813841410940174</v>
+        <v>-0.06204109762882104</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1392666701512926</v>
+        <v>0.1221307783139223</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2294212443587999</v>
+        <v>0.4654425791584146</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9122807017543859</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.02227482471563635</v>
+        <v>-0.02953137989967969</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9503814318660629</v>
+        <v>1.072223905958428</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.9269870146170396</v>
+        <v>0.5133250708558199</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.2534634621863614</v>
+        <v>-0.03349898910258509</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.725172562340744</v>
+        <v>0.9072921918228616</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.111586064624036</v>
+        <v>-0.06316869981712403</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6829,58 +6838,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.09480060127513035</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.03184073837926271</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1155318330023982</v>
+        <v>0.1158491063192834</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1720647483703307</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4372788934221374</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06508110111248899</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.813799478447114</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.1947451936635489</v>
+        <v>-0.03426705224134785</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.07962035925657496</v>
+        <v>0.03039102317395725</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2541315107368404</v>
+        <v>-0.06275100807471734</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6931,68 +6940,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1211277538216655</v>
+        <v>0.04240795586410551</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.05665386735580902</v>
+        <v>-0.06204109762882104</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.0108368102681341</v>
+        <v>-0.3111804093256713</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0007180668185548988</v>
+        <v>0.1221307783139224</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.02126969897940097</v>
+        <v>0.4654425791584145</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.01169590643274854</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3111804093256713</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-0.02953137989967991</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.072223905958429</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.3111804093256713</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1085964261922674</v>
+        <v>0.5133250708558199</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2788819519790349</v>
+        <v>-0.03349898910258509</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2021037747897247</v>
+        <v>0.9072921918228616</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.01083681026813399</v>
+        <v>-0.06316869981712403</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1753808764531287</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.4333713383305771</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.424699586565411</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.3763450826954717</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.2731079632649366</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7041,74 +7046,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1152911046283573</v>
+        <v>0.04240795586410551</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.05115287255705825</v>
+        <v>-0.06204109762882104</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1155336341640988</v>
+        <v>0.1221307783139223</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1729766977443207</v>
+        <v>0.4654425791584146</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2382824194485824</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1036687135184464</v>
+        <v>-0.02953137989967969</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7690714431767565</v>
+        <v>1.072223905958428</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.464179287841805</v>
+        <v>0.5133250708558199</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.04758297514293941</v>
+        <v>-0.03349898910258509</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.8638625555314534</v>
+        <v>0.9072921918228616</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.06316869981712403</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1796738863494852</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.07962035925657385</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2401716894118308</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.01871619665659785</v>
+        <v>0.03548294828386833</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.02949465056512468</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.01871619665659896</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.3763450826954717</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.1002927315345143</v>
-      </c>
+        <v>0.06695233456140093</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7153,58 +7154,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.1570523013067229</v>
+        <v>0.04240795586410551</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2055285913967194</v>
+        <v>-0.06204109762882104</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2005839561652586</v>
+        <v>0.1221307783139223</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1800139898718554</v>
+        <v>0.4654425791584146</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.02227482471563635</v>
+        <v>-0.02953137989967969</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.9503814318660629</v>
+        <v>1.072223905958428</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1947518614956096</v>
+        <v>0.5133250708558199</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2228397008365369</v>
+        <v>-0.03349898910258509</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3624436616901394</v>
+        <v>0.9072921918228616</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.06393443095664597</v>
+        <v>-0.06316869981712403</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.3799896665452887</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3799896665452885</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7259,67 +7260,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.02353552645381107</v>
+        <v>0.04240795586410551</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.035326019967999</v>
+        <v>-0.06204109762882104</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1626106760551097</v>
+        <v>0.1221307783139223</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1994066501341044</v>
+        <v>0.4654425791584146</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.02227482471563635</v>
+        <v>-0.02953137989967969</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9503814318660629</v>
+        <v>1.072223905958428</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4507080064792308</v>
+        <v>0.5133250708558199</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.05634575291400534</v>
+        <v>-0.03349898910258509</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.8387917782499763</v>
+        <v>0.9072921918228616</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.08016850348154003</v>
+        <v>-0.06316869981712403</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.2471625415869563</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.2471625415869563</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.06509411370282026</v>
+        <v>0.03548294828386833</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.07374847887400093</v>
+        <v>-0.02949465056512468</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.009343428835247858</v>
+        <v>0.06695233456140093</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -7367,58 +7368,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1211277538216653</v>
+        <v>0.04240795586410639</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.0566538673558088</v>
+        <v>-0.06204109762882026</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.0108368102681341</v>
+        <v>-0.3111804093256714</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.000718066818554894</v>
+        <v>0.1221307783139222</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.02126969897940076</v>
+        <v>0.4654425791584146</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.01169590643274854</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.3111804093256714</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-0.02953137989968002</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.072223905958429</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.3111804093256714</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1085964261922672</v>
+        <v>0.5133250708558215</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.278881951979035</v>
+        <v>-0.03349898910258409</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2021037747897243</v>
+        <v>0.9072921918228644</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.01083681026813399</v>
+        <v>-0.06316869981712392</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1753808764531288</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.4333713383305771</v>
+        <v>-3.33066907387547e-16</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.4246995865654111</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -7473,67 +7474,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.1152911046283573</v>
+        <v>0.04240795586410551</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.05115287255705825</v>
+        <v>-0.06204109762882104</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1155336341640988</v>
+        <v>0.1221307783139223</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1729766977443207</v>
+        <v>0.4654425791584146</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.2382824194485824</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.1036687135184464</v>
+        <v>-0.02953137989967969</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7690714431767565</v>
+        <v>1.072223905958428</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.464179287841805</v>
+        <v>0.5133250708558199</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04758297514293941</v>
+        <v>-0.03349898910258509</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.8638625555314534</v>
+        <v>0.9072921918228616</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.06316869981712403</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.1796738863494852</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.07962035925657385</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.2401716894118308</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.01871619665659785</v>
+        <v>0.03548294828386833</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.02949465056512468</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.01871619665659896</v>
+        <v>0.06695233456140093</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -7779,28 +7780,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974677</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.103821015825279</v>
+        <v>0.1799741913752893</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005</v>
+        <v>0.2405796270435321</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450099</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7809,10 +7810,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922785</v>
+        <v>0.5373300241682997</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7821,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174769</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7867,49 +7868,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.02506240001890081</v>
+        <v>0.3595704026356366</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.02272081269569726</v>
+        <v>0.2813841410940174</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1047999997493329</v>
+        <v>0.1392666701512926</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3040021784991731</v>
+        <v>0.2294212443587999</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9122807017543859</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.02546035277715153</v>
+        <v>0.02227482471563635</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.91190007874893</v>
+        <v>0.9503814318660629</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2254874204614814</v>
+        <v>0.9269870146170396</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.04698491301235053</v>
+        <v>0.2534634621863614</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7886779214828342</v>
+        <v>1.725172562340744</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07692212197636894</v>
+        <v>-0.111586064624036</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7961,58 +7962,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.02335558522365555</v>
+        <v>0.09480060127513035</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.02100989850384682</v>
+        <v>0.03184073837926271</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07028481312061448</v>
+        <v>0.1155318330023982</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1720647483703307</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184475</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6940712220239806</v>
+        <v>0.769071443176754</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4372788934221374</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.06508110111248899</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.813799478447114</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.001750691321453113</v>
+        <v>-0.1947451936635489</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.0613882756891122</v>
+        <v>0.07962035925657496</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.05618828258578512</v>
+        <v>-0.2541315107368404</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8063,67 +8064,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1211277538216655</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.05665386735580902</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.0108368102681341</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.0007180668185548988</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.02126969897940097</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.01169590643274854</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1085964261922674</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2788819519790349</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2021037747897247</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.01083681026813399</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.04098627743081829</v>
+        <v>-0.1753808764531287</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2641556388316588</v>
+        <v>0.4333713383305771</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1765363018173105</v>
+        <v>-0.424699586565411</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.02318587671251238</v>
+        <v>0.3763450826954717</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.01772738840404031</v>
+        <v>-0.2731079632649366</v>
       </c>
     </row>
     <row r="6">
@@ -8173,73 +8174,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>0.1152911046283573</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>0.05115287255705825</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.1155336341640988</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1729766977443207</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9434697855750487</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485824</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184464</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>0.7690714431767565</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.464179287841805</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.04758297514293941</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.8638625555314534</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.001750691321453335</v>
+        <v>-0.1796738863494852</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.06138827568911243</v>
+        <v>0.07962035925657385</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.05618828258578512</v>
+        <v>-0.2401716894118308</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.01871619665659785</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>0.01871619665659896</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.02318587671251238</v>
+        <v>0.3763450826954717</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.04172379361860035</v>
+        <v>-0.1002927315345143</v>
       </c>
     </row>
     <row r="7">
@@ -8285,68 +8286,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.1570523013067229</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.2055285913967194</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.2005839561652586</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1800139898718554</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.02227482471563635</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.9503814318660629</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1947518614956096</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2228397008365369</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.3624436616901394</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.06393443095664597</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.04098627743081829</v>
+        <v>-0.3799896665452887</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2641556388316588</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1765363018173105</v>
+        <v>-0.3799896665452885</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.02318587671251238</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.01772738840404031</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8395,74 +8392,70 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>0.02353552645381107</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>-0.035326019967999</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.1626106760551097</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1994066501341044</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.02227482471563635</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>0.9503814318660629</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4507080064792308</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.05634575291400534</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.8387917782499763</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348154003</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.001750691321453335</v>
+        <v>-0.2471625415869563</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.06138827568911243</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.05618828258578512</v>
+        <v>-0.2471625415869563</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.06509411370282026</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.07374847887400093</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.02318587671251238</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>0.04172379361860035</v>
-      </c>
+        <v>0.009343428835247858</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8507,68 +8500,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1211277538216653</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.0566538673558088</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.0108368102681341</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.000718066818554894</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.02126969897940076</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>0.01169590643274854</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1085964261922672</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.278881951979035</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2021037747897243</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.01083681026813399</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.04098627743081829</v>
+        <v>-0.1753808764531288</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.2641556388316588</v>
+        <v>0.4333713383305771</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1765363018173105</v>
+        <v>-0.4246995865654111</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.02318587671251238</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.01772738840404031</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8617,74 +8606,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.02335558522365544</v>
+        <v>0.1152911046283573</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.02100989850384671</v>
+        <v>0.05115287255705825</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.07028481312061437</v>
+        <v>0.1155336341640988</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1729766977443207</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9434697855750487</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485824</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184464</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.6940712220239802</v>
+        <v>0.7690714431767565</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.464179287841805</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.04758297514293941</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.8638625555314534</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.001750691321453335</v>
+        <v>-0.1796738863494852</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.06138827568911243</v>
+        <v>0.07962035925657385</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.05618828258578512</v>
+        <v>-0.2401716894118308</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.01871619665659785</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.02318587671251238</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.04172379361860035</v>
-      </c>
+        <v>0.01871619665659896</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8697,7 +8682,1155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947871</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490124</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.02078840693949269</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.02558740810361515</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.2044491165694975</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.1042391861264295</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.3023717680461677</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.2044491165694975</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.02546035277715153</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.91190007874893</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.2044491165694975</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.2308597896818865</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.04978033596571441</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.7816683779068971</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.07692212197636894</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.02027479846139824</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.02507631676042987</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.06992591782126945</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2355679791479366</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6940712220239806</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1602779293212004</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1042692974226319</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.5426851908659128</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>0.0005245122522388179</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.0613882756891122</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.05734354225587934</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.03661639296325592</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.2641556388316588</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1799930632581731</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.01772738840404031</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0.0005245122522388179</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.06138827568911243</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.05734354225587912</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.04172379361860035</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.03661639296325592</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.2641556388316588</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.1799930632581731</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.01772738840404031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.0005245122522388179</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.06138827568911243</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.05734354225587912</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.04172379361860035</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>0.03661639296325592</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.2641556388316588</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1799930632581731</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.01772738840404031</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.02027479846139812</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.02507631676042976</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.06992591782126936</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.2355679791479365</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.6940712220239802</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1602779293212007</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.1042692974226318</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.5426851908659136</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>0.0005245122522388179</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.06138827568911243</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.05734354225587912</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.02318587671251238</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>0.04172379361860035</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8803,12 +9936,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -8817,10 +9946,10 @@
       </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8851,10 +9980,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -8864,7 +9993,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -8897,8 +10026,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -8907,10 +10040,10 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8983,24 +10116,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9031,21 +10160,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.9766081871345029</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9062,30 +10193,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -9115,15 +10248,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -9132,10 +10261,10 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="2" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9162,7 +10291,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -9171,16 +10300,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9207,11 +10334,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -9220,10 +10351,10 @@
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9250,7 +10381,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
@@ -9262,13 +10393,13 @@
         <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9295,22 +10426,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -9330,37 +10459,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="2" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9377,37 +10504,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9434,25 +10559,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9479,11 +10606,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -9492,10 +10623,10 @@
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9522,14 +10653,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -9539,7 +10670,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -9569,30 +10700,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
